--- a/dataset_t6_grouped/results2/G3/G3_T7503_W0058F0002T0006Z000C1N57_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T7503_W0058F0002T0006Z000C1N57_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>58.42741769691367</v>
+        <v>9.494455375748473</v>
       </c>
       <c r="D2" t="n">
-        <v>58.24614958125418</v>
+        <v>9.464999306953805</v>
       </c>
       <c r="E2" t="n">
-        <v>8.42104354334738</v>
+        <v>1.36841957579395</v>
       </c>
       <c r="F2" t="n">
-        <v>7.937203376748098</v>
+        <v>1.289795548721566</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>41.58533061021891</v>
+        <v>6.757616224160573</v>
       </c>
       <c r="D3" t="n">
-        <v>42.37174282775798</v>
+        <v>6.885408209510673</v>
       </c>
       <c r="E3" t="n">
-        <v>8.42104354334738</v>
+        <v>1.36841957579395</v>
       </c>
       <c r="F3" t="n">
-        <v>7.937203376748098</v>
+        <v>1.289795548721566</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
